--- a/Översikt ESKILSTUNA.xlsx
+++ b/Översikt ESKILSTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46108</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>44470</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>45034</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>44789</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>46244</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>46000</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>44581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44953</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>44998</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>44903</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>44657</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>45897</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45379</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>45715</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>45044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45999</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>46199</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>46237</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45798</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45798</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45798</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>45798</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>44502</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>44515</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>44840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44918</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>45414</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45429</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>45849</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>46157</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>46000</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>46009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45992</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>46181</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>45655</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>45120</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>45603</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45849</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43993</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44525</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44803</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44689</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44746</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>44499</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45077</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44525</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>45603</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>44483</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>45217</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>44544</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>44735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>45691</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45012</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44904</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>45957</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>44984</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44886</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45107</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>46065</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>46181</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>46181</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>46181</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>45545</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44522</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>46191</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>46106</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44854</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45229</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>44834</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>45385</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>45103</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>46199</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>45674</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>45832</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>45867</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>44797</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>44473</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>44490</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44470</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>44712</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>44608</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>44513</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44517</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44517</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>44781</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>44588</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>44671</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>44763</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>44533</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>44470</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>44516</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>44754</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>44746</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44683</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>44712</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>44628</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>44799</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>44683</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44746</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>44746</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>44524</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44533</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44468</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>44784</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>44533</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44544</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>44648</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>44628</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44536</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44536</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44781</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>44804</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>44734</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44588</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>44461</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>44578</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>44699</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>44550</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>44482</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>44789</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>44490</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>44722</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>44573</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44844</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>44783</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>44654</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>44490</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>44616</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44578</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>44510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>44643</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>44781</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>44636</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>44782</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44865</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>44748</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>44533</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>44658</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>44804</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45365</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>45005</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>44664</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44755</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44886</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>44946</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45005</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45266</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>44888</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45012</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45544</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45020</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>44516</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>45341</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45622</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45211</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44819</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45514</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>44874</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>45301</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45240</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>44942</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45608</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>44634</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45007</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44525</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44768</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>44582</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44729</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>44889</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>44886</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45163</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44804</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>44844</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>44844</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>44883</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45708</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45266</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>45365</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>45544</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44889</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45041</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44886</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>45006</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>44536</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44889</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         <v>45685</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>44537</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>44516</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>45695</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45695</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45245</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>44915</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>44983</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>45695</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45637</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45245</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45006</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>45062</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45334</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>44858</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>45271</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44930</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45079</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>45049</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>45464</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45036</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45237</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45670</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>45093</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44881</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>45715</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44799</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>45093</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>45582</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44616</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44626</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>44979</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>45103</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45833</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>44490</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44499</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45889</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45889</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>44490</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45897</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45945</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45897</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>45897</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>45901</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45898</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>44634</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>44946</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>46140</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>44804</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45910</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44701</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44873</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>44928</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44946</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45198</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45537</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45341</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45103</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>45670</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>44953</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45225</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45931</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>44965</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>44839</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44965</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>44861</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44998</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45058</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45170</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>44904</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>45407</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45950</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45953</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45953</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44626</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>46150</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>45119</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44803</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44803</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45303</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45303</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45209</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45209</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45004</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45750</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45604</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45146</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45974</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>44467</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45979</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45979</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45979</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45166</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45077</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45303</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>46157</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45061</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45715</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>46161</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45897</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45756</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>44732</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45643</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>46162</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44837</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45518</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>44917</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>45994</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>45953</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45999</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>44671</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>45999</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45435</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46164</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45953</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45965</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>44468</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44942</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>44572</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44797</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>46154</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45429</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44916</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44832</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>44588</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>45387</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>44804</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>45974</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>44918</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>45107</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>44729</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>45363</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45664</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45093</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>44966</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45587</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>46048</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45950</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45103</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45103</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>44956</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>46177</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45429</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44938</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44851</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>45069</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>46069</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>44606</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>46181</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>46181</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45611</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44998</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44915</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>44966</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>46085</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>44865</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>44592</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45464</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>46181</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45531</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>46190</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>46191</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>46044</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45266</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45266</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>46044</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>44499</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>44536</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>46191</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>46043</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45713</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>44617</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>46084</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44482</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>46108</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>46197</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>44739</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>46108</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44964</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>46108</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>46108</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>44930</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>46199</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>44889</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>46083</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45905</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45608</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>44698</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>46199</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>46245</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>46245</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>46125</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>46244</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>45387</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>44852</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>44729</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>46246</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45918</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44741</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45992</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>45267</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45267</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45974</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45329</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>45190</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>45183</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>44851</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>45723</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>45363</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45622</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44515</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>46164</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>46157</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44664</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>44789</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>45229</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>45303</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>44917</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>44903</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>44473</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44886</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>44571</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>45303</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>45303</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>45303</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>46254</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>45763</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35454,7 +35454,7 @@
         <v>44739</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>46254</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35605,7 +35605,7 @@
         <v>46216</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>45167</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>46216</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>44638</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>45210</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>46213</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36043,7 +36043,7 @@
         <v>46217</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>46217</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>44525</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>44497</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>46219</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45182</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>44749</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>44946</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45159</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44746</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>45056</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45071</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>45183</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>45615</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>46092</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>46279</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45642</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>45737</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45365</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44953</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>45642</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>44593</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>45049</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>46237</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37860,7 +37860,7 @@
         <v>46238</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37933,7 +37933,7 @@
         <v>46238</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38011,7 +38011,7 @@
         <v>46239</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>46241</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38157,7 +38157,7 @@
         <v>45798</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45798</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>45798</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45798</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45798</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45798</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>45568</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45568</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45798</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38844,7 +38844,7 @@
         <v>45826</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45826</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38990,7 +38990,7 @@
         <v>45826</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>45826</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>45694</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>45604</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>45460</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45875</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>43993</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44959</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45217</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>45282</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>45798</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>45798</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>45686</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39954,7 +39954,7 @@
         <v>45504</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>45826</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>46125</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>46199</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>46199</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>

--- a/Översikt ESKILSTUNA.xlsx
+++ b/Översikt ESKILSTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46108</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>44470</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>45034</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44789</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>46244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44916</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>46000</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>45229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>44581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44903</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44953</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44998</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>44657</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>45715</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45798</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45798</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>45897</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45999</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>46199</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46237</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>46286</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45044</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>45798</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45798</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>44502</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45849</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>45992</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>45414</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>46009</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>46157</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>44918</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45849</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46181</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>44840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>46000</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44515</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45120</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>45655</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>45429</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>45603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>43993</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44525</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44803</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>44689</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44746</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44499</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45385</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45229</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>44854</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45691</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>46065</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>46106</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45957</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>44735</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45832</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44904</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>44483</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>46181</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>46181</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>46181</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44984</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44525</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>46191</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45603</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>45107</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45103</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>45217</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>44886</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>46199</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44544</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>44522</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45545</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>46287</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45077</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>45012</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>45674</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44797</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44473</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44490</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44470</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44712</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44608</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>44517</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44517</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>44513</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44781</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>44588</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>44671</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44763</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>44533</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>44470</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44516</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44754</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>44746</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>44683</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>44712</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>44628</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44799</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44683</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44746</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>44746</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>44524</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44533</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44468</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>44784</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>44533</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>44648</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44544</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44588</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>44628</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>44536</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44536</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44781</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44804</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>44734</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44588</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>44578</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>44699</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44515</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>44550</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44722</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44482</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44789</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>44490</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>44573</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44844</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>44783</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44654</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>44490</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>44616</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>44578</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44643</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>44781</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>44636</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44782</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44865</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>44748</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44533</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44658</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>44804</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45334</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>44739</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45245</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45429</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45041</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>44851</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45229</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>44799</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>44852</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>44858</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45387</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>45363</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44903</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45464</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45464</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>44979</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>44881</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44883</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45798</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44626</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45798</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45798</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>45798</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>44499</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45604</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>45798</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45798</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45798</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45012</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44515</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44886</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44886</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45889</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45889</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44571</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45568</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44837</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>44634</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>44915</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>44915</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45568</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45897</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45898</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45897</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>44918</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45897</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44588</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45901</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>46048</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>44889</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45950</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45544</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45910</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44930</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45750</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>46069</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>44616</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>44889</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44617</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45931</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44638</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>46085</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>46044</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45036</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>46044</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45209</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45363</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>44928</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45266</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44739</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45093</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45950</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44956</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>44698</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44998</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>44946</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>44946</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>46108</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45953</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45953</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>46108</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>46108</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>46108</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45905</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>44746</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>45365</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45006</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45365</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>44946</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>46125</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>44983</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>44917</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45119</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45974</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45005</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45979</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45979</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45979</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>44741</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>45974</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44499</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>44516</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>45833</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45182</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45918</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>45670</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45163</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45994</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44804</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45713</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>45999</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>44832</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>44482</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45992</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45945</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45965</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>44886</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44525</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45826</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44473</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45826</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45826</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45077</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>46140</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>44671</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>44701</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45826</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44467</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45103</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45103</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45267</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>45267</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>44965</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45587</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44516</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44916</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>44888</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>44865</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>46150</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45756</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>44664</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>44729</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45211</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45407</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>46157</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45429</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45056</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45079</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45715</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45897</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>46162</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45953</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>46161</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>45694</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>44490</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>46164</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45245</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>44889</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45622</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44930</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>46154</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45953</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45974</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>44497</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45099</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>44966</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45604</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>45049</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>45303</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>45608</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>46177</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45007</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46181</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46181</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45271</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>44536</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>46181</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>45582</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>44525</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45460</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>46190</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45544</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45146</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>46191</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>46191</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>46043</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>45875</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>46197</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>46199</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>46084</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45069</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>44626</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>46199</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>45190</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>45435</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45071</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>46083</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>46164</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>44490</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>44572</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>46157</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44606</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45093</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45643</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>45387</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>45107</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45210</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>46213</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>46254</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>46254</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45093</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>46216</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>46217</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>46217</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>46216</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>44886</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45183</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45237</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45685</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>46219</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>44664</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45723</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>45240</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>44729</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>45266</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44749</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>45303</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>45303</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45159</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>44755</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45715</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>44768</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>45225</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44966</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44804</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32712,7 +32712,7 @@
         <v>44917</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>46092</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44998</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45266</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>45531</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>45537</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>44582</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46237</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>44803</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>44803</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44537</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>46279</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>46238</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>46238</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>46239</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>44839</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45763</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>46241</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>44874</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>44938</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>46245</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>46245</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>46287</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>46244</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45103</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34567,7 +34567,7 @@
         <v>46287</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>45005</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>45166</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44942</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34859,7 +34859,7 @@
         <v>46246</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>44819</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>44468</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>45608</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>45062</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>46289</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>45006</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45622</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>44964</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45004</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>44851</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45198</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>44729</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>44904</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44946</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44889</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>44592</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45061</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>44797</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45329</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>44953</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>45303</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45170</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45303</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>44804</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45167</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>44732</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45103</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45664</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45266</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45518</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>45708</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45303</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45303</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>44873</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>44965</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>44634</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45209</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>44844</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>44844</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>44942</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>45514</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45058</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>44789</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45341</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45695</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45020</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45341</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>45695</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>45695</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>45637</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>45301</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>45611</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45670</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>44536</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38924,7 +38924,7 @@
         <v>45615</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45183</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45642</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>44953</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>45642</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39309,7 +39309,7 @@
         <v>45737</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>44593</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45365</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>45049</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>43993</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>44959</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39752,7 +39752,7 @@
         <v>45217</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         <v>45282</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45798</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45798</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45686</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45504</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>45826</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>46125</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46199</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>46199</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>

--- a/Översikt ESKILSTUNA.xlsx
+++ b/Översikt ESKILSTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46108</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>44470</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>45034</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44789</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>46244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44916</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>46000</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>45229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>44581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44903</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44953</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>44998</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>44657</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>45715</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45798</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45798</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>45897</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45999</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>46199</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>46237</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>46286</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45044</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>45798</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45798</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>44502</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45849</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>45992</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>45414</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>46009</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>46157</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>44918</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45849</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46181</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>44840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>46000</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44515</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45120</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>45655</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>45429</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>45603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>43993</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44525</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44803</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>44689</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44746</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44499</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45385</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45229</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>44854</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45691</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>46065</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>46106</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45957</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>44735</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45832</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44904</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>44483</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45867</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>46181</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>46181</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>46181</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44984</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44525</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>46191</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45603</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>45107</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45103</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>45217</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>44886</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>46199</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44544</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>44522</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45545</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>46287</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45077</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>45012</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>45674</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44797</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44473</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44490</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44470</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44712</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44608</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>44517</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44517</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>44513</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44781</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>44588</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>44671</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44763</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>44533</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>44470</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44516</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44754</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>44746</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>44683</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>44712</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>44628</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44799</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44683</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44746</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>44746</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>44524</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44533</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44468</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>44784</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>44533</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>44648</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44544</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44588</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>44628</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>44536</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44536</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44781</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44804</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>44734</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44588</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>44578</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>44699</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44515</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>44550</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44722</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44482</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44789</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>44490</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>44573</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44844</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>44783</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44654</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>44490</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>44616</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>44578</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44643</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>44781</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>44636</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44782</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44865</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>44748</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44533</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44658</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>44804</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45334</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>44739</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45245</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45429</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45041</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>44851</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45229</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>44799</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>44852</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>44858</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45387</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>45363</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44903</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45464</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45464</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>44979</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>44881</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44883</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45798</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>44626</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45798</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45798</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>45798</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>44499</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45604</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>45798</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45798</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45798</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45012</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44515</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44886</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44886</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45889</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45889</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44571</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45568</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44837</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>44634</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>44915</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>44915</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45568</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45897</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45898</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45897</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>44918</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45897</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44588</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45901</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>46048</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>44889</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45950</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45544</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45910</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44930</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45750</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>46069</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>44616</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>44889</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44617</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45931</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>44638</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>46085</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>46044</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45036</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>46044</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45209</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45363</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>44928</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45266</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44739</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45093</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45950</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44956</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>44698</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44998</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>44946</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>44946</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>46108</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45953</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45953</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>46108</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>46108</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>46108</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45905</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>44746</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>45365</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45006</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45365</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>44946</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>46125</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>44983</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>44917</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45119</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45974</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45005</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45979</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45979</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45979</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>44741</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>45974</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44499</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>44516</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>45833</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45182</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45918</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>45670</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45163</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45994</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44804</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45713</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>45999</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>44832</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>44482</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45992</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45945</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45965</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>44886</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44525</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45826</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44473</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45826</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45826</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45077</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>46140</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>44671</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>44701</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45826</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44467</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45103</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45103</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45267</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>45267</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>44965</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45587</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44516</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44916</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>44888</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>44865</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>46150</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45756</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>44664</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>44729</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45211</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45407</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>46157</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45429</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45056</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45079</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45715</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45897</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>46162</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45953</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>46161</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>45694</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>44490</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>46164</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45245</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>44889</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45622</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44930</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>46154</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45953</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45974</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>44497</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45099</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>44966</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45604</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>45049</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>45303</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>45608</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>46177</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45007</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46181</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46181</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45271</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>44536</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>46181</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>45582</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>44525</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45460</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>46190</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45544</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45146</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>46191</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>46191</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>46043</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>45875</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>46197</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>46199</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>46084</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45069</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>44626</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>46199</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>45190</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>45435</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45071</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>46083</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>46164</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>44490</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>44572</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>46157</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44606</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45093</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45643</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>45387</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>45107</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45210</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>46213</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>46254</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>46254</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45093</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>46216</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>46217</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>46217</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>46216</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>44886</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45183</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45237</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45685</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>46219</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>44664</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45723</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>45240</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>44729</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>45266</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44749</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>45303</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>45303</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45159</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>44755</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45715</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>44768</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>45225</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44966</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44804</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32712,7 +32712,7 @@
         <v>44917</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>46092</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44998</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45266</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>45531</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>45537</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>44582</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46237</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>44803</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>44803</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44537</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>46279</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>46238</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>46238</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>46239</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>44839</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45763</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>46241</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>44874</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>44938</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>46245</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>46245</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>46287</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>46244</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45103</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34567,7 +34567,7 @@
         <v>46287</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>45005</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>45166</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44942</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34859,7 +34859,7 @@
         <v>46246</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>44819</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>44468</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>45608</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>45062</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>46289</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>45006</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45622</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>44964</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45004</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>44851</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45198</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>44729</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>44904</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44946</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44889</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>44592</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45061</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>44797</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45329</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>44953</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>45303</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45170</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45303</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>44804</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45167</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>44732</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45103</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45664</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45266</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45518</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>45708</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45303</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45303</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>44873</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>44965</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>44634</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45209</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>44844</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>44844</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>44942</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>45514</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45058</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>44789</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45341</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45695</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45020</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45341</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>45695</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>45695</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>45637</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>45301</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>45611</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45670</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>44536</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38924,7 +38924,7 @@
         <v>45615</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45183</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45642</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>44953</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>45642</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39309,7 +39309,7 @@
         <v>45737</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>44593</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45365</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>45049</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>43993</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>44959</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39752,7 +39752,7 @@
         <v>45217</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         <v>45282</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45798</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45798</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45686</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45504</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>45826</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>46125</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46199</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>46199</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>

--- a/Översikt ESKILSTUNA.xlsx
+++ b/Översikt ESKILSTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46108</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45034</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>45063</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>44916</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>44789</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>46000</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>46296</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>46296</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44581</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44953</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>45194</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>44903</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>44657</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45897</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45798</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45798</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>45999</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45715</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>46199</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>46237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>46286</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>46296</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>45798</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45798</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>44515</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45603</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46009</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>44840</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45849</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>44918</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45992</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45414</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45429</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>45849</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>46157</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>46000</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>45655</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45120</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>43993</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>44803</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>44689</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44746</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>44499</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45077</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45691</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>44483</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>46065</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45217</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44544</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>45957</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>44735</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>46106</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45832</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45012</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44904</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>46181</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44984</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>46181</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>46181</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44886</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>46191</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>45107</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>46199</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45545</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44522</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>46287</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44854</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>45229</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>44834</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45385</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45103</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45674</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44797</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44473</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>44490</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44608</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44712</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44517</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>44517</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44513</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>44781</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44588</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44671</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44763</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44533</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>44516</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44754</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44746</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>44683</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44712</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44628</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44799</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>44683</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>44746</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44746</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44524</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44533</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44533</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>44784</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44648</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44544</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44628</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44536</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44536</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>44781</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44804</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44734</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44588</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>44578</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44699</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>44515</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>44550</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>44722</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>44482</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44789</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>44490</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44573</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44844</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44783</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44654</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44490</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>44616</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44578</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44510</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>44643</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44636</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44782</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44781</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44865</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44748</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44533</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44658</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44804</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45005</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45365</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44664</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>44755</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>44886</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44946</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45005</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45266</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44888</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45012</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45544</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45020</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45341</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45737</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45365</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>44953</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45642</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>44593</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45049</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44516</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45622</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44819</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45514</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44874</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45211</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45608</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44768</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45240</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45301</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44942</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45965</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44626</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>44525</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>44634</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45007</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>45889</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>45889</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44582</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44889</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>44886</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>44729</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45897</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45897</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45901</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45898</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45163</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44804</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44844</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44844</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>44883</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45910</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45708</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>46048</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45798</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45798</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45798</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45798</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45798</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45798</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45568</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>45568</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>45798</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45266</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>45544</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>45950</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>45365</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>45041</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>45931</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44889</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>45006</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>44886</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>44536</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>44889</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>46069</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>45685</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>44537</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>44516</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>45695</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45695</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45245</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45950</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>45953</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45953</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44915</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>46085</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>44983</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45695</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45637</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>46044</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>46044</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45245</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45006</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45062</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45334</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45271</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44930</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44858</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45079</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45049</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45974</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45464</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45979</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45979</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45979</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>46108</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>46108</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45237</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45670</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>46108</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>46108</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45905</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45093</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>44881</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>45826</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45826</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45715</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>44799</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>45826</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>45093</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>46125</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>45582</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>45994</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44616</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45999</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45826</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>44979</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45103</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>44490</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45918</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45992</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45974</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44634</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>44946</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45694</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44873</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44928</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45833</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>44946</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>45198</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>45945</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45537</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45341</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>45103</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45670</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>44953</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45225</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>44965</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>44839</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>46140</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44804</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44965</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>45604</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>44861</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44701</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44998</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>45058</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45170</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44904</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45407</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>44626</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45119</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>44803</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44803</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>46150</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45303</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>45303</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45209</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45209</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45004</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45750</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>46157</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45715</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45604</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>45897</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45460</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>45146</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45875</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>46162</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45953</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45166</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>46164</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45953</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45077</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>46154</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45303</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45061</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45974</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45756</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44732</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44490</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45643</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>44499</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>46177</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44837</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>45518</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>44917</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>46181</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>46181</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>44671</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>46181</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>46190</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>46191</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45435</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>46191</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>46043</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44942</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44572</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>44797</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>46199</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>46083</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>46199</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>45429</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44916</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>44832</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44588</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45387</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         <v>46164</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>46157</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31505,7 +31505,7 @@
         <v>44804</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
         <v>44918</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>45107</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44729</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>45363</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         <v>45664</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45093</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>46216</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44966</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>45587</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>46216</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>46213</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>46217</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>46217</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>46219</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45103</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45103</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>44956</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45429</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>44938</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>44851</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45069</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44606</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>46092</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45611</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44998</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44915</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>44966</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>46279</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>44865</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>46237</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>46238</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>44592</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>46238</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45464</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>46239</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45531</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>46241</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45266</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45266</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>44499</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>44536</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45713</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>44617</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44482</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>46287</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44739</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>46244</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44964</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44930</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>46287</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>46245</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35371,7 +35371,7 @@
         <v>46246</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>44889</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45608</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>44698</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>46245</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45387</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>44852</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44729</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>46289</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>44741</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45267</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>45267</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>45329</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>45190</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>46084</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>45183</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44851</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45723</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>45363</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>46254</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45622</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>44515</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>44664</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>46254</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>44789</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45229</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45303</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>44917</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>44903</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44473</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>44886</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>44571</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45303</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45303</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>45303</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45763</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>44739</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>45167</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>44638</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45210</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44525</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>44497</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45182</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>44749</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>44946</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>45159</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>44746</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45056</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>45071</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45183</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45615</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45642</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>43993</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44959</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45217</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45282</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45798</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45798</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39695,7 +39695,7 @@
         <v>45686</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>45504</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45826</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>46125</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>46199</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>46199</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>

--- a/Översikt ESKILSTUNA.xlsx
+++ b/Översikt ESKILSTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46108</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45034</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>45063</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>44916</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>44789</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>46000</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>46296</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>46296</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44581</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44953</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>45194</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>44903</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>44657</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45897</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45798</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45798</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>45999</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45715</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>46199</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>46237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>46286</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>46296</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>45798</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45798</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>44515</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45603</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46009</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>44840</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45849</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>44918</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45992</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45414</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45429</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>45849</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>46157</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>46181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>46000</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>45655</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45120</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>43993</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>44803</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>44689</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44746</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>44499</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45077</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45691</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>44483</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>46065</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45217</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44544</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>45957</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>44735</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>46106</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45832</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45012</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44904</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>46181</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44984</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>46181</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>46181</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44886</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>46191</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>45107</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>46199</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45545</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44522</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>46287</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44854</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>45229</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>44834</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45385</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45103</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45674</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44797</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44473</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>44490</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44608</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44712</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44517</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>44517</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44513</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>44781</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44588</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44671</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44763</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44533</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>44516</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44754</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44746</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>44683</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44712</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44628</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44799</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>44683</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>44746</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44746</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44524</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44533</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44533</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>44784</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44648</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44544</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44628</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44536</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44536</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>44781</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44804</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44734</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44588</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>44578</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44699</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>44515</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>44550</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>44722</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>44482</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44789</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>44490</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44573</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44844</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44783</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44654</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44490</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>44616</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44578</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44510</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>44643</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44636</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44782</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44781</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44865</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44748</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44533</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44658</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44804</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45005</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45365</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44664</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>44755</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>44886</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44946</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45005</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45266</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44888</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45012</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45544</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45020</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45341</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45737</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45365</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>44953</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45642</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>44593</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45049</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44516</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45622</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44819</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45514</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44874</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45211</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45608</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44768</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45240</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45301</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44942</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45965</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44626</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>44525</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>44634</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45007</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>45889</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>45889</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44582</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44889</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>44886</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>44729</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45897</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45897</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45901</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45898</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45163</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44804</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44844</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44844</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>44883</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45910</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45708</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>46048</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45798</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45798</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45798</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45798</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45798</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45798</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45568</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>45568</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>45798</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45266</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>45544</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>45950</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>45365</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>45041</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>45931</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>44889</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>45006</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>44886</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>44536</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>44889</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>46069</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>45685</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>44537</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>44516</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>45695</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45695</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45245</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45950</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>45953</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45953</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44915</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>46085</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>44983</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45695</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45637</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>46044</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>46044</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45245</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45006</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45062</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45334</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45271</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44930</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>44858</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45079</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45049</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45974</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45464</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45979</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45979</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45979</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>46108</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>46108</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45237</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45670</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>46108</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>46108</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45905</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45093</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>44881</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>45826</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45826</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45715</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>44799</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>45826</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>45093</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>46125</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>45582</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>45994</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44616</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45999</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45826</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>44979</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45103</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>44490</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45918</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45992</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45974</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44634</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>44946</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45694</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44873</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44928</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45833</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>44946</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>45198</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>45945</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45537</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45341</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>45103</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45670</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>44953</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45225</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>44965</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>44839</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>46140</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44804</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44965</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>45604</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>44861</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44701</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44998</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>45058</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45170</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44904</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45407</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>44626</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45119</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>44803</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44803</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>46150</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45303</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>45303</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45209</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45209</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45004</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45750</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>46157</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45715</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45604</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>45897</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45460</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>45146</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45875</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>46162</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45953</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45166</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>46164</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45953</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45077</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>46154</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45303</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45061</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45974</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45756</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44732</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44490</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45643</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>44499</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>46177</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44837</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>45518</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>44917</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>46181</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>46181</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>44671</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>46181</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>46190</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>46191</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45435</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>46191</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>46043</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>44942</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44572</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>44797</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>46199</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>46083</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>46199</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>45429</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44916</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>44832</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44588</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45387</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         <v>46164</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>46157</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31505,7 +31505,7 @@
         <v>44804</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
         <v>44918</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>45107</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44729</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>45363</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         <v>45664</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45093</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>46216</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44966</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>45587</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>46216</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>46213</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>46217</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>46217</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>46219</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45103</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45103</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>44956</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45429</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>44938</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>44851</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45069</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44606</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>46092</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45611</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44998</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>44915</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>44966</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>46279</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>44865</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>46237</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>46238</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>44592</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>46238</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45464</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>46239</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45531</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>46241</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45266</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45266</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>44499</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>44536</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45713</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>44617</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44482</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>46287</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44739</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>46244</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44964</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44930</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>46287</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>46245</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35371,7 +35371,7 @@
         <v>46246</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>44889</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45608</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>44698</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>46245</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45387</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>44852</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44729</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>46289</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>44741</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45267</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>45267</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>45329</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>45190</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>46084</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>45183</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44851</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45723</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>45363</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>46254</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45622</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>44515</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>44664</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>46254</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>44789</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45229</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45303</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>44917</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>44903</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44473</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>44886</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>44571</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45303</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45303</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>45303</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45763</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>44739</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>45167</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>44638</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45210</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44525</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>44497</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45182</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>44749</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>44946</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>45159</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>44746</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45056</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>45071</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45183</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45615</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45642</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>43993</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44959</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45217</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45282</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45798</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45798</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39695,7 +39695,7 @@
         <v>45686</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>45504</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45826</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>46125</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>46199</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>46199</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>

--- a/Översikt ESKILSTUNA.xlsx
+++ b/Översikt ESKILSTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46108</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45063</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>45034</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>44789</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>46000</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>46296</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>46296</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44581</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44953</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44903</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45194</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>44998</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>44657</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45715</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45897</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45798</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45999</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45044</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>46199</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>46237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>46286</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>46296</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>45798</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45798</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>44515</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45120</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44918</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45655</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>45429</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45849</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45603</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>44840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45849</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>45414</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>46009</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>45992</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>46157</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>46181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>46181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>46000</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>43993</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>44803</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>44689</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44746</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44499</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44582</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45385</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44904</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45229</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45012</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>44834</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44483</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44854</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45691</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44984</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44525</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45674</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45603</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>45107</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>45832</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>45957</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45103</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45217</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>45867</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44886</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>44544</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>44735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>46106</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>44522</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45545</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>45077</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>46065</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>46181</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>46181</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>46181</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>46191</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>46199</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>46287</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44797</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44490</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>44712</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44608</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44517</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44517</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>44513</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44781</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>44588</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44671</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44763</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44533</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44516</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>44754</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44746</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44683</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44712</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44799</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44628</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44683</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>44746</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>44746</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44524</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44533</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44784</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44533</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>44482</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44578</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44789</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44573</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44490</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44648</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44578</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>44544</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44588</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44510</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44844</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>44628</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44643</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44536</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44536</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44783</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44654</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>44781</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>44699</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>44781</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44734</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>44804</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>44636</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44782</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>44490</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>44588</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44865</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>44515</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44616</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44550</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44533</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44748</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44722</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44888</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44658</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44592</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45061</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44865</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44797</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45329</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44804</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45756</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44664</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45429</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44729</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>44851</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45211</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44858</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>44953</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45041</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45245</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45407</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>45303</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45334</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45170</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45303</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>44804</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45167</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45429</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45056</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45229</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44732</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44799</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>45103</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44739</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45664</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45079</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44852</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45266</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45518</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>45708</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>44861</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>44490</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45245</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>44889</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45387</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45622</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45363</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>44903</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>44930</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45303</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45303</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>45464</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>44490</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>44873</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44965</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44979</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45464</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>44634</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45209</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>44626</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>44499</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44881</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>44844</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>44844</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>44942</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>44497</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45099</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>44883</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45889</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>45889</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45514</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45058</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>44789</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45341</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44966</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>45604</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>45898</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>45012</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44515</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45901</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>44886</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>44886</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44571</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45695</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44837</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45049</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45303</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45608</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45020</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45341</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45695</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45695</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45637</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44634</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44915</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44915</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45301</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45611</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45670</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>44918</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45007</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>44536</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>44588</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45615</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45183</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45910</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44889</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45271</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>44536</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45544</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45642</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44930</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45582</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44953</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45642</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44525</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45737</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45544</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>45146</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44593</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45365</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45049</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45750</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>44616</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44889</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44617</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44638</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45069</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45931</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44626</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45190</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45798</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45798</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45798</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45798</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45798</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45798</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45798</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45036</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45568</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>45435</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45568</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45071</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45209</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>45363</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>44572</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44928</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>44606</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45266</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45093</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>45643</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45387</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44739</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>45093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45107</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44956</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44698</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44998</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44946</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44946</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45210</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>44746</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45365</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45006</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45365</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>45950</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45826</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>44946</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45826</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45826</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45093</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45826</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44983</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44917</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45119</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>44886</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>45183</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>45237</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45953</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45953</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45005</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45685</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44664</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45723</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>45240</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44729</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45266</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>44749</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44741</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45694</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44499</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44516</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45303</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45303</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45182</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45670</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>45163</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>45159</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45974</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44755</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45715</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45713</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>44768</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44832</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45225</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44966</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>45604</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44804</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>44917</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>45979</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>44482</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>45460</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>45979</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>45979</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>45875</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>44998</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44886</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44525</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>45266</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45531</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45537</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>44582</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45077</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>44803</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>44803</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>44537</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44671</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>46108</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44839</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45103</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45103</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>46108</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>46108</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>46108</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45763</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45267</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45267</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45905</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>44965</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45587</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44516</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>44916</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45994</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>46125</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>44874</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>45999</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>44938</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>45103</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>45005</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>45166</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44942</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45974</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>44819</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45833</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>45608</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45918</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45062</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>45965</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>44804</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45622</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44964</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45004</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45992</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44851</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45945</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>45198</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>46048</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>44729</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>46140</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>44904</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44701</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>44946</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44889</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>45950</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>46069</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>46150</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>46085</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35454,7 +35454,7 @@
         <v>46157</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>46044</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35600,7 +35600,7 @@
         <v>46044</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>45715</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45897</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>46162</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>45953</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>46164</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>46154</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>45953</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>45974</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>46177</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>46181</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>46181</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>46181</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>46190</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>46191</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>46191</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>46043</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>46199</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>46199</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>46083</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>46164</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>46157</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>46213</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37289,7 +37289,7 @@
         <v>46216</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>46217</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>46217</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>46216</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>46219</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37669,7 +37669,7 @@
         <v>46092</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>46237</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>46279</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>46238</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>46238</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>46239</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>46241</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>46245</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>46245</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>46287</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>46244</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>46287</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>46246</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>46289</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>46084</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>46254</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>46254</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>43993</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>44959</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45217</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45282</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45798</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>45798</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45686</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45504</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45826</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>46125</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>46199</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>46199</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>

--- a/Översikt ESKILSTUNA.xlsx
+++ b/Översikt ESKILSTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46108</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45063</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>45034</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>44789</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46244</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>46000</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>46296</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>46296</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44581</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44953</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44903</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45194</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>44998</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>44657</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45715</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45897</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45798</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45798</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45999</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45044</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>46199</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>46237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>46286</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>46296</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>45798</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45798</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>44515</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45120</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44918</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45655</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>45429</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45849</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45603</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>44840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45849</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>45414</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>46009</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>45992</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>46157</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>46181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>46181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>46000</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>43993</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>44803</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>44689</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>44746</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44499</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44582</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45385</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44904</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45229</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45012</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>44834</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44483</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44854</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45691</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44984</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44525</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45674</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>45603</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>45107</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>45832</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>45957</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45103</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45217</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>45867</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44886</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>44544</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>44735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>46106</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>44522</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45545</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>45077</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>46065</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>46181</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>46181</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>46181</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>46191</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>46199</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>46287</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44797</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44490</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>44712</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>44608</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44517</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44517</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>44513</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44781</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>44588</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44671</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44763</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44533</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44516</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>44754</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44746</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44683</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44712</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44799</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44628</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44683</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>44746</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>44746</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44524</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44533</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44784</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44533</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>44482</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44578</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44789</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44573</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44490</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44648</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44578</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>44544</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44588</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44510</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44844</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>44628</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44643</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44536</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44536</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44783</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44654</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>44781</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>44699</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>44781</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44734</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>44804</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>44636</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44782</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>44490</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>44588</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44865</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>44515</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44616</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44550</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44533</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44748</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>44722</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44888</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44658</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44592</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45061</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44865</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44797</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45329</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44804</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45756</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44664</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45429</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44729</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>44851</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45211</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44858</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>44953</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45041</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45245</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45407</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>45303</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45334</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45170</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45303</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>44804</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45167</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45429</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45056</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45229</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44732</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44799</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>45103</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44739</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45664</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45079</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44852</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45266</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45518</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>45708</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>44861</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>44490</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45245</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>44889</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45387</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45622</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45363</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>44903</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>44930</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45303</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45303</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>45464</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>44490</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>44873</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44965</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44979</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45464</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>44634</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45209</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>44626</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>44499</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44881</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>44844</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>44844</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>44942</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>44497</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45099</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>44883</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45889</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>45889</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45514</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45058</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>44789</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45341</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44966</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>45604</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>45898</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>45012</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44515</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45901</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>44886</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>44886</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44571</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45695</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44837</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45049</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45303</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45608</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45020</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45341</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45695</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45695</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45637</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44634</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44915</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44915</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45301</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45611</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45670</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>44918</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45007</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>44536</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>44588</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45615</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45183</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45910</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44889</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45271</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>44536</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45544</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45642</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44930</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45582</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>44953</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45642</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44525</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45737</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45544</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>45146</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44593</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45365</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45049</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45750</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>44616</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44889</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44617</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44638</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45069</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45931</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44626</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45190</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45798</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45798</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45798</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45798</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45798</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45798</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45798</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45036</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45568</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>45435</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45568</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45071</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45209</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>45363</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>44572</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44928</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>44606</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45266</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45093</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>45643</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45387</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44739</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>45093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45107</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44956</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44698</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44998</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44946</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44946</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45210</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>44746</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45365</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45006</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45365</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>45950</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45826</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>44946</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45826</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45826</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45093</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45826</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44983</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44917</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45119</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>44886</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>45183</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>45237</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45953</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45953</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45005</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45685</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44664</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45723</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>45240</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44729</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45266</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>44749</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44741</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45694</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44499</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44516</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45303</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45303</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45182</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45670</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>45163</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>45159</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45974</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44755</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45715</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45713</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>44768</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44832</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45225</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44966</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>45604</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44804</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>44917</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>45979</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>44482</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>45460</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>45979</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>45979</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>45875</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>44998</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44886</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44525</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>45266</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45531</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45537</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>44582</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45077</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>44803</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>44803</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>44537</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44671</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>46108</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44839</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45103</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45103</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>46108</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>46108</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>46108</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45763</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45267</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45267</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45905</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>44965</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45587</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44516</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>44916</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45994</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>46125</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>44874</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>45999</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>44938</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>45103</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>45005</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>45166</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44942</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45974</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>44819</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45833</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>45608</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45918</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45062</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>45965</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>44804</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45622</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44964</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45004</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45992</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>44851</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45945</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>45198</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>46048</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>44729</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>46140</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>44904</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>44701</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>44946</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44889</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>45950</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>46069</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>46150</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>46085</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35454,7 +35454,7 @@
         <v>46157</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>46044</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35600,7 +35600,7 @@
         <v>46044</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>45715</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45897</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>46162</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>45953</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>46164</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>46154</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>45953</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>45974</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>46177</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>46181</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>46181</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>46181</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>46190</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>46191</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>46191</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>46043</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>46199</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>46199</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>46083</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>46164</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>46157</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>46213</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37289,7 +37289,7 @@
         <v>46216</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>46217</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>46217</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>46216</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>46219</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37669,7 +37669,7 @@
         <v>46092</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>46237</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>46279</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>46238</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>46238</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>46239</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>46241</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>46245</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>46245</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>46287</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>46244</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>46287</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>46246</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>46289</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>46084</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>46254</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>46254</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>43993</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>44959</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45217</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45282</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45798</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>45798</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45686</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45504</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45826</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>46125</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>46199</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>46199</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>

--- a/Översikt ESKILSTUNA.xlsx
+++ b/Översikt ESKILSTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46108</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,75 +1202,196 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
+          <t>A 33004-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ESKILSTUNA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>15</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp
+Älg
+Hasselticka
+Svart trolldruva
+Tibast
+Blåsippa
+Spillkråka
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0484/artfynd/A 33004-2026 artfynd.xlsx", "A 33004-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor/A 33004-2026 karta.png", "A 33004-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor_geotiff/A 33004-2026 georefererad karta.tif", "A 33004-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomål/A 33004-2026 FSC-klagomål.docx", "A 33004-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomålsmail/A 33004-2026 FSC-klagomål mail.docx", "A 33004-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsyn/A 33004-2026 tillsynsbegäran.docx", "A 33004-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsynsmail/A 33004-2026 tillsynsbegäran mail.docx", "A 33004-2026")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0484/fåglar/A 33004-2026 prioriterade fågelarter.docx", "A 33004-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>A 17144-2023</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>45034</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ESKILSTUNA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E8" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ESKILSTUNA</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>3.8</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>4</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>5</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S8" t="n">
         <v>7</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>54</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>48</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Dropptaggsvamp
@@ -1281,120 +1402,120 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/artfynd/A 17144-2023 artfynd.xlsx", "A 17144-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor/A 17144-2023 karta.png", "A 17144-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor_geotiff/A 17144-2023 georefererad karta.tif", "A 17144-2023")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/knärot/A 17144-2023 karta knärot.png", "A 17144-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomål/A 17144-2023 FSC-klagomål.docx", "A 17144-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomålsmail/A 17144-2023 FSC-klagomål mail.docx", "A 17144-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsyn/A 17144-2023 tillsynsbegäran.docx", "A 17144-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsynsmail/A 17144-2023 tillsynsbegäran mail.docx", "A 17144-2023")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/fåglar/A 17144-2023 prioriterade fågelarter.docx", "A 17144-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 4219-2023</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>44953</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ESKILSTUNA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="E9" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ESKILSTUNA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" t="n">
         <v>0.6</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K9" t="n">
         <v>3</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>7</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>10</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>7</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Tallkötticka
@@ -1405,115 +1526,115 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/artfynd/A 4219-2023 artfynd.xlsx", "A 4219-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor/A 4219-2023 karta.png", "A 4219-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor_geotiff/A 4219-2023 georefererad karta.tif", "A 4219-2023")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/knärot/A 4219-2023 karta knärot.png", "A 4219-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomål/A 4219-2023 FSC-klagomål.docx", "A 4219-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomålsmail/A 4219-2023 FSC-klagomål mail.docx", "A 4219-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsyn/A 4219-2023 tillsynsbegäran.docx", "A 4219-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsynsmail/A 4219-2023 tillsynsbegäran mail.docx", "A 4219-2023")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/fåglar/A 4219-2023 prioriterade fågelarter.docx", "A 4219-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 21734-2023</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>45063</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ESKILSTUNA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESKILSTUNA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>10.5</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>6</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>6</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>7</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>10</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>10</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Kryddspindling
@@ -1524,107 +1645,107 @@
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/artfynd/A 21734-2023 artfynd.xlsx", "A 21734-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor/A 21734-2023 karta.png", "A 21734-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor_geotiff/A 21734-2023 georefererad karta.tif", "A 21734-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomål/A 21734-2023 FSC-klagomål.docx", "A 21734-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomålsmail/A 21734-2023 FSC-klagomål mail.docx", "A 21734-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsyn/A 21734-2023 tillsynsbegäran.docx", "A 21734-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsynsmail/A 21734-2023 tillsynsbegäran mail.docx", "A 21734-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 61503-2022</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>44916</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ESKILSTUNA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ESKILSTUNA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>1.8</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>5</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>6</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>6</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>13</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Jungfrulin
@@ -1634,107 +1755,107 @@
 Svinrot</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/artfynd/A 61503-2022 artfynd.xlsx", "A 61503-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor/A 61503-2022 karta.png", "A 61503-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor_geotiff/A 61503-2022 georefererad karta.tif", "A 61503-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomål/A 61503-2022 FSC-klagomål.docx", "A 61503-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomålsmail/A 61503-2022 FSC-klagomål mail.docx", "A 61503-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsyn/A 61503-2022 tillsynsbegäran.docx", "A 61503-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsynsmail/A 61503-2022 tillsynsbegäran mail.docx", "A 61503-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 33699-2022</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>44789</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ESKILSTUNA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ESKILSTUNA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>6.5</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>4</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S12" t="n">
         <v>6</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>9</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>5</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
@@ -1744,159 +1865,40 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/artfynd/A 33699-2022 artfynd.xlsx", "A 33699-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor/A 33699-2022 karta.png", "A 33699-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor_geotiff/A 33699-2022 georefererad karta.tif", "A 33699-2022")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/knärot/A 33699-2022 karta knärot.png", "A 33699-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomål/A 33699-2022 FSC-klagomål.docx", "A 33699-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomålsmail/A 33699-2022 FSC-klagomål mail.docx", "A 33699-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsyn/A 33699-2022 tillsynsbegäran.docx", "A 33699-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsynsmail/A 33699-2022 tillsynsbegäran mail.docx", "A 33699-2022")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0484/fåglar/A 33699-2022 prioriterade fågelarter.docx", "A 33699-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 33004-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ESKILSTUNA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Hasselticka
-Tibast
-Blåsippa
-Spillkråka
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0484/artfynd/A 33004-2026 artfynd.xlsx", "A 33004-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor/A 33004-2026 karta.png", "A 33004-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0484/kartor_geotiff/A 33004-2026 georefererad karta.tif", "A 33004-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomål/A 33004-2026 FSC-klagomål.docx", "A 33004-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0484/klagomålsmail/A 33004-2026 FSC-klagomål mail.docx", "A 33004-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsyn/A 33004-2026 tillsynsbegäran.docx", "A 33004-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0484/tillsynsmail/A 33004-2026 tillsynsbegäran mail.docx", "A 33004-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0484/fåglar/A 33004-2026 prioriterade fågelarter.docx", "A 33004-2026")</f>
         <v/>
       </c>
     </row>
@@ -1920,7 +1922,7 @@
         <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2034,7 +2036,7 @@
         <v>46000</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2148,7 +2150,7 @@
         <v>46296</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2266,7 +2268,7 @@
         <v>46296</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2384,7 +2386,7 @@
         <v>44581</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2497,7 +2499,7 @@
         <v>44953</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2618,7 +2620,7 @@
         <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2735,7 +2737,7 @@
         <v>45194</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2851,7 +2853,7 @@
         <v>44903</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2959,7 +2961,7 @@
         <v>44657</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3077,7 @@
         <v>45897</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3189,7 @@
         <v>45715</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3294,7 +3296,7 @@
         <v>45044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3401,7 +3403,7 @@
         <v>45999</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3521,7 +3523,7 @@
         <v>44930</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3637,7 +3639,7 @@
         <v>46199</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3749,7 +3751,7 @@
         <v>46237</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3861,7 +3863,7 @@
         <v>46286</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3968,7 +3970,7 @@
         <v>46296</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4080,7 +4082,7 @@
         <v>45798</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4192,7 +4194,7 @@
         <v>45798</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4306,7 @@
         <v>45798</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,7 +4418,7 @@
         <v>45798</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4528,7 +4530,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4639,7 +4641,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4745,7 +4747,7 @@
         <v>44515</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4856,7 +4858,7 @@
         <v>44840</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4966,7 +4968,7 @@
         <v>44918</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5072,7 +5074,7 @@
         <v>45414</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5183,7 +5185,7 @@
         <v>45429</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5289,7 +5291,7 @@
         <v>45849</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5404,7 +5406,7 @@
         <v>46157</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5510,7 +5512,7 @@
         <v>46009</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5616,7 +5618,7 @@
         <v>46181</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5731,7 +5733,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5842,7 +5844,7 @@
         <v>45992</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5948,7 +5950,7 @@
         <v>45655</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6059,7 +6061,7 @@
         <v>46000</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6170,7 +6172,7 @@
         <v>45120</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6281,7 +6283,7 @@
         <v>45603</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6387,7 +6389,7 @@
         <v>45849</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6502,7 +6504,7 @@
         <v>43993</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6612,7 +6614,7 @@
         <v>44525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6718,7 +6720,7 @@
         <v>44803</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6823,7 +6825,7 @@
         <v>44689</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6928,7 +6930,7 @@
         <v>44746</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7038,7 +7040,7 @@
         <v>44582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7148,7 +7150,7 @@
         <v>44499</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7253,7 +7255,7 @@
         <v>45077</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7358,7 +7360,7 @@
         <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7463,7 +7465,7 @@
         <v>45603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7568,7 +7570,7 @@
         <v>45217</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7677,7 +7679,7 @@
         <v>44544</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7782,7 +7784,7 @@
         <v>44735</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7891,7 +7893,7 @@
         <v>45691</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8005,7 +8007,7 @@
         <v>45012</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8115,7 +8117,7 @@
         <v>45957</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8220,7 +8222,7 @@
         <v>44904</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8325,7 +8327,7 @@
         <v>44984</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8430,7 +8432,7 @@
         <v>44886</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8539,7 +8541,7 @@
         <v>46181</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8649,7 +8651,7 @@
         <v>46181</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8754,7 +8756,7 @@
         <v>46181</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8868,7 +8870,7 @@
         <v>46065</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8973,7 +8975,7 @@
         <v>45107</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9087,7 +9089,7 @@
         <v>46191</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9192,7 +9194,7 @@
         <v>46106</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9297,7 +9299,7 @@
         <v>45545</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9406,7 +9408,7 @@
         <v>44522</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9516,7 +9518,7 @@
         <v>46199</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9626,7 +9628,7 @@
         <v>44854</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9735,7 +9737,7 @@
         <v>45229</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9840,7 +9842,7 @@
         <v>46287</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9945,7 +9947,7 @@
         <v>44834</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10054,7 +10056,7 @@
         <v>45385</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10164,7 +10166,7 @@
         <v>45103</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10269,7 +10271,7 @@
         <v>45674</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10374,7 +10376,7 @@
         <v>45832</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10484,7 +10486,7 @@
         <v>45867</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10589,7 +10591,7 @@
         <v>44797</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10662,7 +10664,7 @@
         <v>44490</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10735,7 +10737,7 @@
         <v>44712</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10808,7 +10810,7 @@
         <v>44608</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10881,7 +10883,7 @@
         <v>44517</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10954,7 +10956,7 @@
         <v>44517</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11027,7 +11029,7 @@
         <v>44513</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11100,7 +11102,7 @@
         <v>44781</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11173,7 +11175,7 @@
         <v>44588</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11251,7 +11253,7 @@
         <v>44763</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11324,7 +11326,7 @@
         <v>44671</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11397,7 +11399,7 @@
         <v>44533</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11470,7 +11472,7 @@
         <v>44516</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11543,7 +11545,7 @@
         <v>44754</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11621,7 +11623,7 @@
         <v>44746</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11694,7 +11696,7 @@
         <v>44683</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11772,7 +11774,7 @@
         <v>44712</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11845,7 +11847,7 @@
         <v>44628</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11918,7 +11920,7 @@
         <v>44799</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11991,7 +11993,7 @@
         <v>44683</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12064,7 +12066,7 @@
         <v>44746</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12137,7 +12139,7 @@
         <v>44746</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12210,7 +12212,7 @@
         <v>44524</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12283,7 +12285,7 @@
         <v>44533</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12356,7 +12358,7 @@
         <v>44784</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12429,7 +12431,7 @@
         <v>44533</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12502,7 +12504,7 @@
         <v>44648</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12575,7 +12577,7 @@
         <v>44588</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12648,7 +12650,7 @@
         <v>44544</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12721,7 +12723,7 @@
         <v>44628</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12794,7 +12796,7 @@
         <v>44536</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12867,7 +12869,7 @@
         <v>44536</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12940,7 +12942,7 @@
         <v>44781</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13013,7 +13015,7 @@
         <v>44804</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13086,7 +13088,7 @@
         <v>44734</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13159,7 +13161,7 @@
         <v>44588</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13232,7 +13234,7 @@
         <v>44578</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13305,7 +13307,7 @@
         <v>44699</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13383,7 +13385,7 @@
         <v>44515</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13461,7 +13463,7 @@
         <v>44550</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13534,7 +13536,7 @@
         <v>44722</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13612,7 +13614,7 @@
         <v>44789</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13685,7 +13687,7 @@
         <v>44573</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13758,7 +13760,7 @@
         <v>44490</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13831,7 +13833,7 @@
         <v>44844</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13904,7 +13906,7 @@
         <v>44783</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13977,7 +13979,7 @@
         <v>44654</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14050,7 +14052,7 @@
         <v>44490</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14123,7 +14125,7 @@
         <v>44616</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14196,7 +14198,7 @@
         <v>44578</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14269,7 +14271,7 @@
         <v>44510</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14342,7 +14344,7 @@
         <v>44643</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14415,7 +14417,7 @@
         <v>44781</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14488,7 +14490,7 @@
         <v>44636</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14561,7 +14563,7 @@
         <v>44782</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14634,7 +14636,7 @@
         <v>44865</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14712,7 +14714,7 @@
         <v>44533</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14785,7 +14787,7 @@
         <v>44748</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14858,7 +14860,7 @@
         <v>44658</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14936,7 +14938,7 @@
         <v>44804</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15009,7 +15011,7 @@
         <v>45365</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15082,7 +15084,7 @@
         <v>45099</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15155,7 +15157,7 @@
         <v>45005</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15228,7 +15230,7 @@
         <v>44755</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15301,7 +15303,7 @@
         <v>44886</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15374,7 +15376,7 @@
         <v>44664</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15452,7 +15454,7 @@
         <v>44946</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15525,7 +15527,7 @@
         <v>45005</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15598,7 +15600,7 @@
         <v>45266</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15671,7 +15673,7 @@
         <v>44888</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15744,7 +15746,7 @@
         <v>45012</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15822,7 +15824,7 @@
         <v>45544</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15895,7 +15897,7 @@
         <v>45020</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15968,7 +15970,7 @@
         <v>45341</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16041,7 +16043,7 @@
         <v>44819</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16114,7 +16116,7 @@
         <v>45514</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16187,7 +16189,7 @@
         <v>44874</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16260,7 +16262,7 @@
         <v>45240</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16333,7 +16335,7 @@
         <v>45608</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16411,7 +16413,7 @@
         <v>44768</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16489,7 +16491,7 @@
         <v>45211</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16562,7 +16564,7 @@
         <v>45301</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16635,7 +16637,7 @@
         <v>44942</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16708,7 +16710,7 @@
         <v>44516</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16781,7 +16783,7 @@
         <v>44634</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16854,7 +16856,7 @@
         <v>45007</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16927,7 +16929,7 @@
         <v>45622</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17000,7 +17002,7 @@
         <v>44525</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17073,7 +17075,7 @@
         <v>44729</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17151,7 +17153,7 @@
         <v>44582</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17224,7 +17226,7 @@
         <v>44889</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17297,7 +17299,7 @@
         <v>44886</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17370,7 +17372,7 @@
         <v>45163</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17443,7 +17445,7 @@
         <v>44844</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17516,7 +17518,7 @@
         <v>44844</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17589,7 +17591,7 @@
         <v>44883</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17662,7 +17664,7 @@
         <v>44804</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17735,7 +17737,7 @@
         <v>45708</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17808,7 +17810,7 @@
         <v>45266</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17881,7 +17883,7 @@
         <v>45544</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17954,7 +17956,7 @@
         <v>45365</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18027,7 +18029,7 @@
         <v>44889</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18100,7 +18102,7 @@
         <v>45041</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18173,7 +18175,7 @@
         <v>44886</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18246,7 +18248,7 @@
         <v>44536</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18324,7 +18326,7 @@
         <v>44889</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18397,7 +18399,7 @@
         <v>45685</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18470,7 +18472,7 @@
         <v>44537</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18543,7 +18545,7 @@
         <v>44516</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18616,7 +18618,7 @@
         <v>45695</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18689,7 +18691,7 @@
         <v>45695</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18762,7 +18764,7 @@
         <v>45245</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18840,7 +18842,7 @@
         <v>44915</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18913,7 +18915,7 @@
         <v>45695</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18986,7 +18988,7 @@
         <v>45006</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19059,7 +19061,7 @@
         <v>45637</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19132,7 +19134,7 @@
         <v>44983</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19205,7 +19207,7 @@
         <v>45245</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19283,7 +19285,7 @@
         <v>45006</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19356,7 +19358,7 @@
         <v>45062</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19429,7 +19431,7 @@
         <v>45334</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19502,7 +19504,7 @@
         <v>44858</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19575,7 +19577,7 @@
         <v>45271</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19648,7 +19650,7 @@
         <v>45079</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19721,7 +19723,7 @@
         <v>44930</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19794,7 +19796,7 @@
         <v>45049</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19867,7 +19869,7 @@
         <v>45464</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19940,7 +19942,7 @@
         <v>45036</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20013,7 +20015,7 @@
         <v>45237</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20086,7 +20088,7 @@
         <v>45670</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20164,7 +20166,7 @@
         <v>45093</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20237,7 +20239,7 @@
         <v>44881</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20310,7 +20312,7 @@
         <v>44626</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20383,7 +20385,7 @@
         <v>45833</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20456,7 +20458,7 @@
         <v>45715</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20529,7 +20531,7 @@
         <v>44799</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20602,7 +20604,7 @@
         <v>45093</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20675,7 +20677,7 @@
         <v>45582</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20748,7 +20750,7 @@
         <v>44490</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20821,7 +20823,7 @@
         <v>44616</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20894,7 +20896,7 @@
         <v>44499</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20967,7 +20969,7 @@
         <v>45889</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21045,7 +21047,7 @@
         <v>45889</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21123,7 +21125,7 @@
         <v>45945</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21196,7 +21198,7 @@
         <v>44979</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21269,7 +21271,7 @@
         <v>45103</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21342,7 +21344,7 @@
         <v>45901</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21415,7 +21417,7 @@
         <v>45898</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21488,7 +21490,7 @@
         <v>46140</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21561,7 +21563,7 @@
         <v>44804</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21634,7 +21636,7 @@
         <v>44701</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21707,7 +21709,7 @@
         <v>44490</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21780,7 +21782,7 @@
         <v>45910</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21853,7 +21855,7 @@
         <v>44634</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21926,7 +21928,7 @@
         <v>44946</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21999,7 +22001,7 @@
         <v>44873</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22072,7 +22074,7 @@
         <v>44928</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22145,7 +22147,7 @@
         <v>44946</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22218,7 +22220,7 @@
         <v>45931</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22291,7 +22293,7 @@
         <v>46150</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22364,7 +22366,7 @@
         <v>45198</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22437,7 +22439,7 @@
         <v>45537</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22510,7 +22512,7 @@
         <v>45341</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22583,7 +22585,7 @@
         <v>45103</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22661,7 +22663,7 @@
         <v>45670</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22734,7 +22736,7 @@
         <v>44953</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22812,7 +22814,7 @@
         <v>45225</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22885,7 +22887,7 @@
         <v>44965</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22958,7 +22960,7 @@
         <v>44839</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23031,7 +23033,7 @@
         <v>45950</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23104,7 +23106,7 @@
         <v>45953</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23177,7 +23179,7 @@
         <v>45953</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23250,7 +23252,7 @@
         <v>44965</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23328,7 +23330,7 @@
         <v>44861</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23406,7 +23408,7 @@
         <v>44998</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23484,7 +23486,7 @@
         <v>45058</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23557,7 +23559,7 @@
         <v>46157</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23630,7 +23632,7 @@
         <v>45715</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23703,7 +23705,7 @@
         <v>45170</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23776,7 +23778,7 @@
         <v>44904</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23854,7 +23856,7 @@
         <v>45897</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23927,7 +23929,7 @@
         <v>45407</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24000,7 +24002,7 @@
         <v>46162</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24073,7 +24075,7 @@
         <v>44626</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24146,7 +24148,7 @@
         <v>45974</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24219,7 +24221,7 @@
         <v>45119</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24297,7 +24299,7 @@
         <v>44803</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24370,7 +24372,7 @@
         <v>44803</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24443,7 +24445,7 @@
         <v>45979</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24516,7 +24518,7 @@
         <v>45979</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24589,7 +24591,7 @@
         <v>45979</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24662,7 +24664,7 @@
         <v>45953</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24735,7 +24737,7 @@
         <v>45303</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24808,7 +24810,7 @@
         <v>45303</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24881,7 +24883,7 @@
         <v>45209</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24954,7 +24956,7 @@
         <v>45209</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25027,7 +25029,7 @@
         <v>45004</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25100,7 +25102,7 @@
         <v>46164</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25173,7 +25175,7 @@
         <v>45750</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25246,7 +25248,7 @@
         <v>45604</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25319,7 +25321,7 @@
         <v>45146</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25397,7 +25399,7 @@
         <v>45953</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25470,7 +25472,7 @@
         <v>45994</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25543,7 +25545,7 @@
         <v>45999</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25616,7 +25618,7 @@
         <v>46154</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25689,7 +25691,7 @@
         <v>45166</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25762,7 +25764,7 @@
         <v>45077</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25835,7 +25837,7 @@
         <v>45303</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25908,7 +25910,7 @@
         <v>45061</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25986,7 +25988,7 @@
         <v>45974</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26059,7 +26061,7 @@
         <v>45756</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26137,7 +26139,7 @@
         <v>45965</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26210,7 +26212,7 @@
         <v>44732</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26283,7 +26285,7 @@
         <v>45643</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26356,7 +26358,7 @@
         <v>44837</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26434,7 +26436,7 @@
         <v>45518</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26512,7 +26514,7 @@
         <v>44917</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26585,7 +26587,7 @@
         <v>44671</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26658,7 +26660,7 @@
         <v>46177</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26731,7 +26733,7 @@
         <v>45435</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26804,7 +26806,7 @@
         <v>46048</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26877,7 +26879,7 @@
         <v>45950</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26950,7 +26952,7 @@
         <v>46181</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27023,7 +27025,7 @@
         <v>46181</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27096,7 +27098,7 @@
         <v>44942</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27169,7 +27171,7 @@
         <v>44572</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27242,7 +27244,7 @@
         <v>44797</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27315,7 +27317,7 @@
         <v>45429</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27388,7 +27390,7 @@
         <v>46069</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27461,7 +27463,7 @@
         <v>44916</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27534,7 +27536,7 @@
         <v>44832</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27607,7 +27609,7 @@
         <v>46181</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27680,7 +27682,7 @@
         <v>44588</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27753,7 +27755,7 @@
         <v>45387</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27826,7 +27828,7 @@
         <v>46190</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27899,7 +27901,7 @@
         <v>44804</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27972,7 +27974,7 @@
         <v>46191</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28045,7 +28047,7 @@
         <v>46085</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28118,7 +28120,7 @@
         <v>44918</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28191,7 +28193,7 @@
         <v>45107</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28269,7 +28271,7 @@
         <v>44729</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28347,7 +28349,7 @@
         <v>45363</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28425,7 +28427,7 @@
         <v>46044</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28498,7 +28500,7 @@
         <v>46044</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28571,7 +28573,7 @@
         <v>46191</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28644,7 +28646,7 @@
         <v>45664</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28722,7 +28724,7 @@
         <v>45093</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28795,7 +28797,7 @@
         <v>46043</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28868,7 +28870,7 @@
         <v>44966</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28941,7 +28943,7 @@
         <v>45587</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29014,7 +29016,7 @@
         <v>45103</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29087,7 +29089,7 @@
         <v>45103</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29160,7 +29162,7 @@
         <v>46108</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29233,7 +29235,7 @@
         <v>46108</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29306,7 +29308,7 @@
         <v>46108</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29379,7 +29381,7 @@
         <v>46108</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29452,7 +29454,7 @@
         <v>44956</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29525,7 +29527,7 @@
         <v>45429</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29598,7 +29600,7 @@
         <v>44938</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29671,7 +29673,7 @@
         <v>46199</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29749,7 +29751,7 @@
         <v>44851</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29822,7 +29824,7 @@
         <v>45069</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29895,7 +29897,7 @@
         <v>46083</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29968,7 +29970,7 @@
         <v>46199</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30046,7 +30048,7 @@
         <v>46125</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30124,7 +30126,7 @@
         <v>44606</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30202,7 +30204,7 @@
         <v>45611</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30275,7 +30277,7 @@
         <v>44998</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30348,7 +30350,7 @@
         <v>44915</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30421,7 +30423,7 @@
         <v>44966</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30494,7 +30496,7 @@
         <v>44865</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30572,7 +30574,7 @@
         <v>44592</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30645,7 +30647,7 @@
         <v>45464</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30718,7 +30720,7 @@
         <v>45918</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30791,7 +30793,7 @@
         <v>45992</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30864,7 +30866,7 @@
         <v>45974</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30937,7 +30939,7 @@
         <v>46164</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31010,7 +31012,7 @@
         <v>46157</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31083,7 +31085,7 @@
         <v>45531</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31156,7 +31158,7 @@
         <v>45266</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31229,7 +31231,7 @@
         <v>45266</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31302,7 +31304,7 @@
         <v>44499</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31375,7 +31377,7 @@
         <v>44536</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31448,7 +31450,7 @@
         <v>45713</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31526,7 +31528,7 @@
         <v>44617</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31599,7 +31601,7 @@
         <v>46216</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31672,7 +31674,7 @@
         <v>46216</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31745,7 +31747,7 @@
         <v>44739</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31818,7 +31820,7 @@
         <v>46213</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31891,7 +31893,7 @@
         <v>46217</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31969,7 +31971,7 @@
         <v>46217</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32047,7 +32049,7 @@
         <v>44964</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32120,7 +32122,7 @@
         <v>44930</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32193,7 +32195,7 @@
         <v>46219</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32271,7 +32273,7 @@
         <v>44889</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32344,7 +32346,7 @@
         <v>45608</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32422,7 +32424,7 @@
         <v>44698</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32500,7 +32502,7 @@
         <v>46092</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32573,7 +32575,7 @@
         <v>45387</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32651,7 +32653,7 @@
         <v>44852</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32724,7 +32726,7 @@
         <v>44729</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32797,7 +32799,7 @@
         <v>46279</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32875,7 +32877,7 @@
         <v>46237</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32953,7 +32955,7 @@
         <v>46238</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33026,7 +33028,7 @@
         <v>46238</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33104,7 +33106,7 @@
         <v>44741</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33177,7 +33179,7 @@
         <v>45267</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33250,7 +33252,7 @@
         <v>45267</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33323,7 +33325,7 @@
         <v>45329</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33401,7 +33403,7 @@
         <v>46239</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33474,7 +33476,7 @@
         <v>45190</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33547,7 +33549,7 @@
         <v>45183</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33625,7 +33627,7 @@
         <v>44851</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33698,7 +33700,7 @@
         <v>45723</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33771,7 +33773,7 @@
         <v>45363</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33849,7 +33851,7 @@
         <v>46241</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33922,7 +33924,7 @@
         <v>45622</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33995,7 +33997,7 @@
         <v>44515</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34068,7 +34070,7 @@
         <v>44664</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34141,7 +34143,7 @@
         <v>44789</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34214,7 +34216,7 @@
         <v>45229</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34292,7 +34294,7 @@
         <v>45303</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34365,7 +34367,7 @@
         <v>46287</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34438,7 +34440,7 @@
         <v>44917</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34511,7 +34513,7 @@
         <v>44903</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34584,7 +34586,7 @@
         <v>46244</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34662,7 +34664,7 @@
         <v>44886</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34735,7 +34737,7 @@
         <v>46287</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34808,7 +34810,7 @@
         <v>46245</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34881,7 +34883,7 @@
         <v>46246</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34954,7 +34956,7 @@
         <v>44571</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35027,7 +35029,7 @@
         <v>45303</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35100,7 +35102,7 @@
         <v>45303</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35173,7 +35175,7 @@
         <v>45303</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35246,7 +35248,7 @@
         <v>45763</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35319,7 +35321,7 @@
         <v>44739</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35392,7 +35394,7 @@
         <v>46245</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35465,7 +35467,7 @@
         <v>45167</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35538,7 +35540,7 @@
         <v>44638</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35611,7 +35613,7 @@
         <v>45210</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35684,7 +35686,7 @@
         <v>46289</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35762,7 +35764,7 @@
         <v>44525</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35835,7 +35837,7 @@
         <v>44497</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35908,7 +35910,7 @@
         <v>45182</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35986,7 +35988,7 @@
         <v>44749</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36059,7 +36061,7 @@
         <v>44946</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36132,7 +36134,7 @@
         <v>45159</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36210,7 +36212,7 @@
         <v>44746</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36283,7 +36285,7 @@
         <v>46254</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36361,7 +36363,7 @@
         <v>46254</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36434,7 +36436,7 @@
         <v>45056</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36512,7 +36514,7 @@
         <v>45071</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36590,7 +36592,7 @@
         <v>45183</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36668,7 +36670,7 @@
         <v>45615</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36741,7 +36743,7 @@
         <v>45642</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36819,7 +36821,7 @@
         <v>45737</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36892,7 +36894,7 @@
         <v>45365</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36965,7 +36967,7 @@
         <v>44953</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37043,7 +37045,7 @@
         <v>45642</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37121,7 +37123,7 @@
         <v>44593</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37194,7 +37196,7 @@
         <v>45049</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37267,7 +37269,7 @@
         <v>45798</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37340,7 +37342,7 @@
         <v>45798</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37413,7 +37415,7 @@
         <v>45798</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37486,7 +37488,7 @@
         <v>45798</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37564,7 +37566,7 @@
         <v>45798</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37642,7 +37644,7 @@
         <v>45798</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37720,7 +37722,7 @@
         <v>45905</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37793,7 +37795,7 @@
         <v>45568</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37871,7 +37873,7 @@
         <v>45568</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37949,7 +37951,7 @@
         <v>45798</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38027,7 +38029,7 @@
         <v>46311</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38100,7 +38102,7 @@
         <v>46310</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38178,7 +38180,7 @@
         <v>46310</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38256,7 +38258,7 @@
         <v>46084</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38329,7 +38331,7 @@
         <v>45826</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38402,7 +38404,7 @@
         <v>45826</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38475,7 +38477,7 @@
         <v>45826</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38548,7 +38550,7 @@
         <v>45826</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38621,7 +38623,7 @@
         <v>45694</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38694,7 +38696,7 @@
         <v>45604</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38767,7 +38769,7 @@
         <v>45460</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38840,7 +38842,7 @@
         <v>45875</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38913,7 +38915,7 @@
         <v>43993</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38991,7 +38993,7 @@
         <v>44959</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39064,7 +39066,7 @@
         <v>45217</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39137,7 +39139,7 @@
         <v>45282</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39210,7 +39212,7 @@
         <v>45798</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39288,7 +39290,7 @@
         <v>45798</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39366,7 +39368,7 @@
         <v>45686</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39439,7 +39441,7 @@
         <v>45504</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39512,7 +39514,7 @@
         <v>45826</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39585,7 +39587,7 @@
         <v>46125</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39663,7 +39665,7 @@
         <v>46199</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39741,7 +39743,7 @@
         <v>46199</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>

--- a/Översikt ESKILSTUNA.xlsx
+++ b/Översikt ESKILSTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46108</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45034</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45063</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>44916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>44789</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>46000</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>46296</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46296</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>44581</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>44953</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44998</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>45194</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>44903</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44657</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45897</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>45715</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>45044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>45999</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>44930</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>46199</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>46237</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>46286</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>46296</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>45798</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45798</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45798</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>45798</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>44515</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>44840</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>44918</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>45414</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>45429</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45849</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>46157</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>46009</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>46181</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>45992</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>45655</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>46000</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45120</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>45603</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>45849</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>43993</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44803</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44689</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44746</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44499</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45077</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>45603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>45217</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44544</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44735</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>45691</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45012</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45957</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44904</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44984</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44886</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>46181</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>46181</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>46181</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>46065</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>45107</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>46191</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>46106</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45545</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44522</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>46199</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>44854</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45229</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>46287</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>44834</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>45385</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>45103</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45674</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45832</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>45867</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44797</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>44490</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44712</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>44608</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>44517</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>44517</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>44513</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44781</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44588</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44763</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44671</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44533</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44516</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44754</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44746</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44683</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44712</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44628</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44799</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44683</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44746</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>44746</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44524</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>44533</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>44784</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44533</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>44648</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44588</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>44544</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>44628</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44536</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44536</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>44781</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>44804</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>44734</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>44588</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>44578</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44699</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44515</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>44550</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44722</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44789</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44573</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44490</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44844</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44783</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44654</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44490</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44616</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44578</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44510</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44643</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44781</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44636</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>44782</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44865</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>44533</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>44748</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>44658</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>44804</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>45365</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45099</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45005</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>44755</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>44886</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>44664</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44946</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>45005</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45266</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>44888</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45012</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45544</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45020</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45341</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>44819</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45514</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44874</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45240</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45608</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44768</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45211</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45301</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>44942</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>44516</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44634</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>45007</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45622</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>44525</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>44729</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44582</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>44889</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>44886</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>45163</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>44844</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>44844</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>44883</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>44804</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45708</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>45266</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>45544</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>45365</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>44889</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45041</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>44886</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>44536</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>44889</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>45685</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>44537</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44516</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45695</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45695</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45245</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>44915</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45695</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45006</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>45637</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>44983</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45245</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45006</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45062</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45334</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44858</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45271</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45079</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44930</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45049</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45464</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45036</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45237</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45670</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45093</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>44881</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44626</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45833</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>45715</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>44799</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45093</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45582</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44490</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>44616</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44499</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>45889</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45889</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>45945</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>44979</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45103</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>45901</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45898</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>46140</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>44804</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44701</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>44490</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45910</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>44634</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44946</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44873</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44928</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44946</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45931</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>46150</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45198</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45537</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45341</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45103</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45670</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44953</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45225</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44965</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>44839</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45950</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45953</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45953</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44965</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>44861</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>44998</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45058</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>46157</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>45715</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45170</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>44904</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45897</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>45407</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>46162</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>44626</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45974</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45119</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>44803</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>44803</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45979</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45979</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45979</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45953</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45303</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45303</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45209</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45209</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>45004</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>46164</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45750</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45604</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45146</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45953</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45994</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>45999</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>46154</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45166</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>45077</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45303</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45061</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45974</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>45756</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>45965</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>44732</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45643</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44837</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45518</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>44917</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44671</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>46177</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45435</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>46048</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45950</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>46181</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>46181</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44942</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>44572</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44797</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>45429</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>46069</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44916</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44832</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>46181</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>44588</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>45387</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>46190</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>44804</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>46191</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>46085</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>44918</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>45107</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>44729</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45363</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>46044</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>46044</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>46191</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>45664</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45093</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>46043</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>44966</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>45587</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>45103</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45103</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>46108</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>46108</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>46108</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>46108</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44956</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>45429</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>44938</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>46199</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>44851</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>45069</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>46083</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>46199</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>46125</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44606</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45611</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>44998</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44915</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>44966</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>44865</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>44592</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>45464</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>45918</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30793,7 +30793,7 @@
         <v>45992</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>45974</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>46164</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>46157</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>45531</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>45266</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45266</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31304,7 +31304,7 @@
         <v>44499</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>44536</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31450,7 +31450,7 @@
         <v>45713</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>44617</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>46216</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>46216</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>44739</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>46213</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>46217</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>46217</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>44964</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>44930</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>46219</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>44889</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>45608</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>44698</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>46092</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45387</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>44852</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>44729</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>46279</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>46237</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>46238</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>46238</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44741</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45267</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45267</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45329</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>46239</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45190</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45183</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>44851</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45723</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45363</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>46241</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45622</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44515</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44664</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>44789</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45229</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45303</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>46287</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44917</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>44903</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>46244</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>44886</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>46287</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>46245</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>46246</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44571</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45303</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45303</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>45303</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45763</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>44739</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>46245</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>45167</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>44638</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45210</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>46289</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44525</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44497</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>45182</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>44749</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44946</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45159</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>44746</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>46254</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>46254</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45056</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45071</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>45183</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>45615</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>45642</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45737</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>45365</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>44953</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45642</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>44593</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45049</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45798</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45798</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>45798</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37488,7 +37488,7 @@
         <v>45798</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45798</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45798</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45905</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45568</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45568</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>45798</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>46311</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>46310</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>46310</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>46084</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45826</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>45826</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>45826</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38550,7 +38550,7 @@
         <v>45826</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45694</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>45604</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45460</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45875</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>43993</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>44959</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         <v>45217</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>45282</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45798</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>45798</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45686</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>45504</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45826</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>46125</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>46199</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>46199</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>

--- a/Översikt ESKILSTUNA.xlsx
+++ b/Översikt ESKILSTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46108</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45063</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>45034</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>44916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>44789</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>46000</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>46296</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46296</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>44581</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>44903</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44953</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45194</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44998</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44657</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45715</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>45897</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>45044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>46199</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45999</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>46237</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>46286</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45798</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45798</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>46296</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44930</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45798</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>45798</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>46181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>46181</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>44515</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45120</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>45655</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>45429</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>46009</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45603</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>46000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>45992</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45849</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46157</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45414</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>44918</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44840</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>43993</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44803</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44689</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44746</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44499</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45691</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45077</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45385</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45229</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>46181</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>46181</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>46181</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>45957</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>45012</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>46191</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>46199</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>44834</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>45674</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>46287</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>44854</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>46065</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>45832</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>46106</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>45867</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>44735</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44904</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44984</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>44525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>45603</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>45107</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>45103</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>45217</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44886</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>44544</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>44522</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>45545</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44797</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>44712</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44608</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>44517</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>44517</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>44513</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>44781</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44588</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>44671</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44763</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44533</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44516</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44754</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44746</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44683</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>44712</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44628</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44799</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44683</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44746</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44746</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>44524</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44533</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>44533</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>44784</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44544</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>44648</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44588</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>44628</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>44536</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44536</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44781</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>44804</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>44734</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>44588</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>44578</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>44699</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44515</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44550</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>44722</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44789</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44573</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44844</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44654</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44783</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44616</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44578</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44510</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44643</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44781</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44636</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44782</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44865</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>44533</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44748</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44658</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>45103</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44804</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45005</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>45166</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>45334</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>45889</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>45889</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44942</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44739</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>44819</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45898</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45608</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45062</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>45901</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>45006</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>44626</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>44499</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>45910</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>45622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45715</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>45897</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>46162</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>45953</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>44964</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>46164</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45004</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>44851</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45198</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>46154</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>45953</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45974</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45931</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>44729</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45429</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44851</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>44904</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>44858</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>44946</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>44889</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>44592</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>45061</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>45041</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45245</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>44797</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45329</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45229</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>44799</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>46177</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>44852</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>44953</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>44861</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46181</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45950</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45303</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45170</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45303</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>46181</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>44804</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45167</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45953</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45953</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44732</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>46181</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45103</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45664</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45266</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45518</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>46190</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45708</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>46191</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45387</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>46191</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>46043</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45303</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45303</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44873</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44965</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45974</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>46199</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>44634</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45209</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>45363</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>44903</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>46199</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45979</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44844</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44844</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>44942</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>45979</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45979</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>46083</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45464</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>46164</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45514</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45058</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44789</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>45341</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>46157</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>44979</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45695</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>46213</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45464</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45020</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45341</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45695</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45695</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45994</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>46216</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>46217</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>46217</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>46216</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45637</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45301</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45611</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45999</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45670</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>46219</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>44536</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45615</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45183</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>46092</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45642</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>44953</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45642</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>46237</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>45965</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45737</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24120,7 +24120,7 @@
         <v>46279</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>46238</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44593</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45365</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45049</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>46238</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44881</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>46239</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>46241</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>46245</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>46245</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45798</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45798</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45798</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>45798</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>46287</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45798</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45798</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45798</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>46244</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>46048</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>45568</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>46287</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45568</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45950</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>46246</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>46289</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>46069</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>44883</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45826</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>45826</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45826</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45826</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>46085</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>46044</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46044</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>46254</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>45604</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>46254</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45694</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45012</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>44515</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>46108</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>46108</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44886</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>44886</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>46108</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>46108</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44571</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45604</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44837</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>46125</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45460</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44634</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45875</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>44915</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>44915</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45905</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44918</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44588</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>44889</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>45544</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45974</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>46310</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45833</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>46310</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>44930</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45918</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>44804</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>45750</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>44616</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>46311</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>46084</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>45992</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>44889</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45945</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44617</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>44638</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>46140</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>44701</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>45036</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>45209</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45363</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30264,7 +30264,7 @@
         <v>44928</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>45266</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>46150</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>44739</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>45093</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>44956</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44698</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>44998</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44946</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44946</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>46157</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>44746</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45365</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>45006</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>45365</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44946</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44983</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>44917</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45119</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>45005</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>44741</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44499</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44516</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45182</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>45670</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45163</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>45713</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44832</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44886</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44525</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32474,7 +32474,7 @@
         <v>45077</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44671</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>45103</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>45103</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45267</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>45267</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44965</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>45587</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44516</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>44916</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>44888</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>44865</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45756</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33433,7 +33433,7 @@
         <v>44664</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>44729</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>45211</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45407</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>45429</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45056</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45079</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>45245</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>44889</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45622</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44930</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>44497</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>45099</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>44966</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45049</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>45303</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>45608</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45007</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45271</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44536</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45582</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>44525</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45544</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45146</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>45069</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>44626</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45190</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45435</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45071</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>44572</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>44606</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45093</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45643</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45387</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>45107</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36043,7 +36043,7 @@
         <v>45210</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>45093</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36189,7 +36189,7 @@
         <v>44886</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>45183</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45237</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45685</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>44664</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>45723</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>45240</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>44729</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45266</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>44749</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45303</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>45303</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>45159</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37153,7 +37153,7 @@
         <v>44755</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>45715</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44768</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45225</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44966</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>44804</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44917</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37669,7 +37669,7 @@
         <v>44998</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>45266</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45531</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>45537</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>44582</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>44803</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44803</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>44537</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>44839</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45763</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44874</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>44938</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38550,7 +38550,7 @@
         <v>43993</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>44959</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>45217</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45282</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>45798</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45798</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45686</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         <v>45504</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>45826</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>46125</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>46199</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>46199</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>

--- a/Översikt ESKILSTUNA.xlsx
+++ b/Översikt ESKILSTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44503</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45217</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46108</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>45904</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>46244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>45063</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>45034</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>44916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>44789</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>46000</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>46296</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46296</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>44581</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>44903</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44953</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45194</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>44998</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44657</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45715</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>45897</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>45044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>46199</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45999</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>46237</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>46286</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45798</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45798</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>46296</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44930</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45798</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>45798</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45849</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>46181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>46181</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>44515</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45120</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>45655</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>45429</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>46009</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45603</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>46000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>45992</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>45849</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46157</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45414</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>44918</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44840</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>43993</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44803</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44689</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44746</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44582</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44499</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45691</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45077</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45385</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45229</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>46181</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>46181</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>46181</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>45957</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>45012</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>46191</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>46199</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>44834</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>45674</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>46287</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>44854</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>46065</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>45832</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>46106</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>45867</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>44735</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44904</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44984</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>44525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>45603</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>45107</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>45103</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>45217</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44886</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>44544</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>44522</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>45545</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44797</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>44712</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44608</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>44517</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>44517</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>44513</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>44781</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44588</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>44671</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44763</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44533</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44516</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44754</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44746</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44683</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>44712</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44628</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44799</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44683</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44746</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44746</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>44524</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44533</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>44533</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>44784</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44544</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>44648</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44588</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>44628</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>44536</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44536</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44781</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>44804</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>44734</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>44588</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>44578</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>44699</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44515</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44550</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>44722</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44789</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44573</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44844</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44654</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44783</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44616</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44578</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44510</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44643</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44781</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44636</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44782</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44865</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>44533</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44748</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44658</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>45103</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>44804</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45005</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>45166</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>45334</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>45889</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>45889</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44942</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44739</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>44819</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45898</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45608</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45062</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>45901</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>45006</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>44626</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>44499</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>45910</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>45622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45715</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>45897</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>46162</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>45953</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>44964</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>46164</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45004</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>44851</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45198</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>46154</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>45953</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45974</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45931</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>44729</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45429</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44851</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>44904</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>44858</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>44946</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>44889</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>44592</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>45061</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>45041</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45245</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>44797</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45329</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45229</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>44799</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>46177</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>44852</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>44953</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>44861</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46181</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45950</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45303</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45170</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45303</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>46181</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>44804</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45167</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45953</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45953</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44732</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>46181</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45103</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45664</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45266</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45518</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>46190</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45708</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>46191</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45387</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>46191</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>46043</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45303</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45303</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44873</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44965</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45974</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>46199</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>44634</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45209</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>45363</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>44903</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>46199</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45979</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44844</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44844</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>44942</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>45979</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45979</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>46083</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45464</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>46164</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45514</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45058</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44789</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>45341</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>46157</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>44979</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45695</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>46213</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45464</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45020</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45341</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45695</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45695</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45994</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>46216</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>46217</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>46217</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>46216</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45637</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45301</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45611</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45999</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45670</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>46219</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>44536</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45615</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45183</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>46092</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45642</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>44953</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45642</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>46237</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>45965</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45737</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24120,7 +24120,7 @@
         <v>46279</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>46238</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44593</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45365</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45049</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>46238</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44881</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>46239</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>46241</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>46245</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>46245</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45798</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45798</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45798</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>45798</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>46287</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45798</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45798</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45798</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>46244</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>46048</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>45568</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>46287</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45568</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45950</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>46246</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>46289</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>46069</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>44883</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45826</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>45826</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45826</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45826</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>46085</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>46044</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>46044</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>46254</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>45604</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>46254</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45694</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45012</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>44515</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>46108</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>46108</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44886</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>44886</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>46108</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>46108</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44571</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45604</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44837</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>46125</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45460</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44634</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45875</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>44915</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>44915</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45905</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44918</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44588</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>44889</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>45544</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45974</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>46310</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45833</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>46310</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>44930</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45918</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>44804</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>45750</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>44616</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>46311</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29456,7 +29456,7 @@
         <v>46084</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>45992</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>44889</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45945</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>44617</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>44638</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>46140</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>44701</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>45036</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>45209</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45363</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30264,7 +30264,7 @@
         <v>44928</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>45266</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>46150</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>44739</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>45093</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>44956</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44698</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>44998</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>44946</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44946</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>46157</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>44746</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45365</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>45006</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>45365</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44946</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44983</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>44917</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45119</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>45005</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>44741</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44499</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44516</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45182</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>45670</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45163</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>45713</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44832</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>44886</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44525</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32474,7 +32474,7 @@
         <v>45077</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44671</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>45103</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>45103</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45267</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>45267</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44965</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>45587</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44516</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>44916</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>44888</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>44865</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45756</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33433,7 +33433,7 @@
         <v>44664</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>44729</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>45211</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45407</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>45429</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45056</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45079</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>45245</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>44889</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45622</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44930</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>44497</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>45099</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>44966</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45049</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>45303</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>45608</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45007</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45271</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44536</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45582</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>44525</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45544</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45146</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>45069</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>44626</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45190</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45435</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45071</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>44572</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>44606</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45093</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45643</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45387</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>45107</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36043,7 +36043,7 @@
         <v>45210</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>45093</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36189,7 +36189,7 @@
         <v>44886</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>45183</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45237</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45685</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>44664</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>45723</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>45240</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>44729</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45266</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>44749</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45303</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>45303</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>45159</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37153,7 +37153,7 @@
         <v>44755</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>45715</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44768</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45225</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44966</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>44804</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44917</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37669,7 +37669,7 @@
         <v>44998</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>45266</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45531</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>45537</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>44582</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>44803</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44803</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>44537</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>44839</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45763</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44874</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>44938</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38550,7 +38550,7 @@
         <v>43993</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>44959</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>45217</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45282</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>45798</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45798</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45686</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         <v>45504</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>45826</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>46125</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>46199</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>46199</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
